--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/89.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/89.xlsx
@@ -426,13 +426,13 @@
         <v>-4.093418622806711</v>
       </c>
       <c r="E2">
-        <v>-21.34917579268896</v>
+        <v>-21.00307810970474</v>
       </c>
       <c r="F2">
-        <v>-0.6127832767336364</v>
+        <v>-0.2907885835914406</v>
       </c>
       <c r="G2">
-        <v>-17.11925091825036</v>
+        <v>-15.26192231217089</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.930162040495611</v>
       </c>
       <c r="E3">
-        <v>-23.32679209115667</v>
+        <v>-21.67242279583048</v>
       </c>
       <c r="F3">
-        <v>-0.6322333433513688</v>
+        <v>-0.004943015540012402</v>
       </c>
       <c r="G3">
-        <v>-16.56647754264886</v>
+        <v>-14.11403864933892</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.782759789927504</v>
       </c>
       <c r="E4">
-        <v>-23.15082917664062</v>
+        <v>-23.20302889652703</v>
       </c>
       <c r="F4">
-        <v>-0.3968560593155005</v>
+        <v>-0.00839896434449194</v>
       </c>
       <c r="G4">
-        <v>-15.87150299395351</v>
+        <v>-15.01679462298832</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-0.7784784087040091</v>
       </c>
       <c r="E5">
-        <v>-23.12508933038102</v>
+        <v>-22.92131252850986</v>
       </c>
       <c r="F5">
-        <v>-0.3226881839058467</v>
+        <v>-0.02984125456595714</v>
       </c>
       <c r="G5">
-        <v>-15.40044712444338</v>
+        <v>-14.43118560145556</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>0.1058181731147536</v>
       </c>
       <c r="E6">
-        <v>-22.53213094381666</v>
+        <v>-24.09356689555743</v>
       </c>
       <c r="F6">
-        <v>-0.7252565175835449</v>
+        <v>-0.3363893807481506</v>
       </c>
       <c r="G6">
-        <v>-14.86973853486113</v>
+        <v>-14.22163965572909</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>0.8509503670816494</v>
       </c>
       <c r="E7">
-        <v>-23.87555257140616</v>
+        <v>-24.73177832288044</v>
       </c>
       <c r="F7">
-        <v>-0.2308429481204516</v>
+        <v>0.07333356218752687</v>
       </c>
       <c r="G7">
-        <v>-13.53888598589195</v>
+        <v>-13.32106036577176</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>1.46484273972406</v>
       </c>
       <c r="E8">
-        <v>-24.59042653520502</v>
+        <v>-25.51653569756566</v>
       </c>
       <c r="F8">
-        <v>0.1191513916037703</v>
+        <v>0.01678506143541863</v>
       </c>
       <c r="G8">
-        <v>-13.62252195312333</v>
+        <v>-12.58150104502627</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>1.940657884511979</v>
       </c>
       <c r="E9">
-        <v>-25.07567969597094</v>
+        <v>-25.35068939398275</v>
       </c>
       <c r="F9">
-        <v>-0.8126393381700592</v>
+        <v>0.2009319634451515</v>
       </c>
       <c r="G9">
-        <v>-13.31309519320427</v>
+        <v>-12.84131596949381</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>2.285773704362983</v>
       </c>
       <c r="E10">
-        <v>-26.42279202987669</v>
+        <v>-25.30476161059696</v>
       </c>
       <c r="F10">
-        <v>-0.1061620568554868</v>
+        <v>0.2266966747744245</v>
       </c>
       <c r="G10">
-        <v>-13.12445368728552</v>
+        <v>-11.85047631068102</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>2.496979046638838</v>
       </c>
       <c r="E11">
-        <v>-26.90540961877015</v>
+        <v>-26.74500201247045</v>
       </c>
       <c r="F11">
-        <v>0.3759983019853962</v>
+        <v>0.2955613420713559</v>
       </c>
       <c r="G11">
-        <v>-12.18358340284249</v>
+        <v>-12.48789536990338</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>2.580510978578201</v>
       </c>
       <c r="E12">
-        <v>-28.25427447211687</v>
+        <v>-27.43025069931113</v>
       </c>
       <c r="F12">
-        <v>0.742726491613571</v>
+        <v>0.6399426642742083</v>
       </c>
       <c r="G12">
-        <v>-11.91927606807816</v>
+        <v>-12.10579551430624</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.545416193191327</v>
       </c>
       <c r="E13">
-        <v>-27.353425137771</v>
+        <v>-29.07134250884682</v>
       </c>
       <c r="F13">
-        <v>0.6729249407840734</v>
+        <v>0.9539784034103065</v>
       </c>
       <c r="G13">
-        <v>-11.90427929678526</v>
+        <v>-10.47682833952569</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>2.404651276028806</v>
       </c>
       <c r="E14">
-        <v>-28.65613578403154</v>
+        <v>-28.855959228094</v>
       </c>
       <c r="F14">
-        <v>1.436045156734673</v>
+        <v>1.200218897566488</v>
       </c>
       <c r="G14">
-        <v>-12.45129066787566</v>
+        <v>-10.32673151532068</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.182113251329612</v>
       </c>
       <c r="E15">
-        <v>-31.01791158951793</v>
+        <v>-28.45338694576012</v>
       </c>
       <c r="F15">
-        <v>1.298281030709893</v>
+        <v>1.388859692736408</v>
       </c>
       <c r="G15">
-        <v>-11.50807651719082</v>
+        <v>-10.81413982452203</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>1.90721270957347</v>
       </c>
       <c r="E16">
-        <v>-30.09572861412193</v>
+        <v>-30.39205836776186</v>
       </c>
       <c r="F16">
-        <v>1.175800283266764</v>
+        <v>1.727524451492541</v>
       </c>
       <c r="G16">
-        <v>-11.47077991114539</v>
+        <v>-9.970053338919598</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.61324374421937</v>
       </c>
       <c r="E17">
-        <v>-32.06833642033715</v>
+        <v>-31.17012945057476</v>
       </c>
       <c r="F17">
-        <v>2.050324317750258</v>
+        <v>1.928830984251265</v>
       </c>
       <c r="G17">
-        <v>-10.18880756706356</v>
+        <v>-10.48112211709013</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.331295938880751</v>
       </c>
       <c r="E18">
-        <v>-31.57935632546291</v>
+        <v>-33.07623661598733</v>
       </c>
       <c r="F18">
-        <v>2.107635744880344</v>
+        <v>2.593236313545054</v>
       </c>
       <c r="G18">
-        <v>-10.51536308960281</v>
+        <v>-10.11787912888467</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.089454950251905</v>
       </c>
       <c r="E19">
-        <v>-32.9177536111409</v>
+        <v>-33.13188024035659</v>
       </c>
       <c r="F19">
-        <v>2.635052300038373</v>
+        <v>2.560621832162032</v>
       </c>
       <c r="G19">
-        <v>-9.81682804917997</v>
+        <v>-9.448791391033653</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.9107521559129925</v>
       </c>
       <c r="E20">
-        <v>-33.26967944017299</v>
+        <v>-32.29860026667917</v>
       </c>
       <c r="F20">
-        <v>2.697264348723421</v>
+        <v>2.622162903250813</v>
       </c>
       <c r="G20">
-        <v>-10.67867892214614</v>
+        <v>-9.17085785082968</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.8051984745375301</v>
       </c>
       <c r="E21">
-        <v>-34.5211843665918</v>
+        <v>-34.09440965492392</v>
       </c>
       <c r="F21">
-        <v>2.801743015768912</v>
+        <v>3.141401815408404</v>
       </c>
       <c r="G21">
-        <v>-10.20037792372331</v>
+        <v>-9.004198367291689</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.7793147639929692</v>
       </c>
       <c r="E22">
-        <v>-34.17139597729132</v>
+        <v>-34.77094102929983</v>
       </c>
       <c r="F22">
-        <v>3.030886006731311</v>
+        <v>3.393469045875877</v>
       </c>
       <c r="G22">
-        <v>-10.12175577771116</v>
+        <v>-9.373469858924155</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.8308070892968128</v>
       </c>
       <c r="E23">
-        <v>-35.12954862173024</v>
+        <v>-35.53162730039729</v>
       </c>
       <c r="F23">
-        <v>3.000634029181073</v>
+        <v>3.471463150319062</v>
       </c>
       <c r="G23">
-        <v>-9.590409908112596</v>
+        <v>-8.984666148609989</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.9469640290934579</v>
       </c>
       <c r="E24">
-        <v>-34.983573262093</v>
+        <v>-35.26787538876854</v>
       </c>
       <c r="F24">
-        <v>3.364406603916059</v>
+        <v>3.624972883936255</v>
       </c>
       <c r="G24">
-        <v>-9.885134535291753</v>
+        <v>-9.215484004699055</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.119094170360712</v>
       </c>
       <c r="E25">
-        <v>-35.08455823246404</v>
+        <v>-35.93650910447508</v>
       </c>
       <c r="F25">
-        <v>3.277290517633246</v>
+        <v>3.478361794049576</v>
       </c>
       <c r="G25">
-        <v>-9.649678604902167</v>
+        <v>-8.240584622657858</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.333464483513283</v>
       </c>
       <c r="E26">
-        <v>-35.79497844207636</v>
+        <v>-36.07396640450391</v>
       </c>
       <c r="F26">
-        <v>3.058129353874581</v>
+        <v>3.28233361838149</v>
       </c>
       <c r="G26">
-        <v>-10.31077137527585</v>
+        <v>-9.095079463435763</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.573749887828775</v>
       </c>
       <c r="E27">
-        <v>-34.94609108273151</v>
+        <v>-35.9669857345467</v>
       </c>
       <c r="F27">
-        <v>3.148229219542278</v>
+        <v>3.562182634804052</v>
       </c>
       <c r="G27">
-        <v>-9.953715796683294</v>
+        <v>-8.924348008884468</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.830339029972742</v>
       </c>
       <c r="E28">
-        <v>-35.54794792072094</v>
+        <v>-35.72371384661765</v>
       </c>
       <c r="F28">
-        <v>3.629361574436286</v>
+        <v>3.911102582006843</v>
       </c>
       <c r="G28">
-        <v>-8.980604109233305</v>
+        <v>-8.649943510225359</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.089454127296359</v>
       </c>
       <c r="E29">
-        <v>-35.57011027251447</v>
+        <v>-35.6980034354391</v>
       </c>
       <c r="F29">
-        <v>3.407768323983002</v>
+        <v>3.541481733408093</v>
       </c>
       <c r="G29">
-        <v>-10.12020313185324</v>
+        <v>-8.930045457757554</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.338914215905375</v>
       </c>
       <c r="E30">
-        <v>-34.73820469069839</v>
+        <v>-35.78763552147292</v>
       </c>
       <c r="F30">
-        <v>3.086756074580526</v>
+        <v>3.829127343825804</v>
       </c>
       <c r="G30">
-        <v>-9.692960677282599</v>
+        <v>-9.236744328152255</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.571161770393387</v>
       </c>
       <c r="E31">
-        <v>-35.39296542628242</v>
+        <v>-35.02221020232643</v>
       </c>
       <c r="F31">
-        <v>2.957063560528625</v>
+        <v>3.377622377460322</v>
       </c>
       <c r="G31">
-        <v>-10.08112214176215</v>
+        <v>-9.030537067602131</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.775800342850655</v>
       </c>
       <c r="E32">
-        <v>-34.47253497032739</v>
+        <v>-34.69114026033667</v>
       </c>
       <c r="F32">
-        <v>2.639793875051997</v>
+        <v>3.28770143915163</v>
       </c>
       <c r="G32">
-        <v>-10.07210090516763</v>
+        <v>-9.370831354129356</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.945979172339885</v>
       </c>
       <c r="E33">
-        <v>-34.50219647507763</v>
+        <v>-35.17937315699964</v>
       </c>
       <c r="F33">
-        <v>2.661989151242607</v>
+        <v>3.423870129558619</v>
       </c>
       <c r="G33">
-        <v>-9.285660949040526</v>
+        <v>-9.517730191343436</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>3.077990363167541</v>
       </c>
       <c r="E34">
-        <v>-33.5004685894999</v>
+        <v>-34.93188299553244</v>
       </c>
       <c r="F34">
-        <v>2.831685183910503</v>
+        <v>3.203295771010778</v>
       </c>
       <c r="G34">
-        <v>-10.14120854329992</v>
+        <v>-9.264238408855903</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>3.166721420585796</v>
       </c>
       <c r="E35">
-        <v>-32.21123241764919</v>
+        <v>-33.29677556439788</v>
       </c>
       <c r="F35">
-        <v>2.787730352783155</v>
+        <v>3.268339179478595</v>
       </c>
       <c r="G35">
-        <v>-10.38207390510067</v>
+        <v>-9.250251353952482</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>3.213436555603254</v>
       </c>
       <c r="E36">
-        <v>-32.47757008793631</v>
+        <v>-33.87095889772644</v>
       </c>
       <c r="F36">
-        <v>2.739862314044983</v>
+        <v>3.274614890922204</v>
       </c>
       <c r="G36">
-        <v>-10.70020408924248</v>
+        <v>-9.411316015529103</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>3.220499572419265</v>
       </c>
       <c r="E37">
-        <v>-32.10764810319773</v>
+        <v>-31.97805223404622</v>
       </c>
       <c r="F37">
-        <v>2.959169270466541</v>
+        <v>3.232991085666334</v>
       </c>
       <c r="G37">
-        <v>-10.3850434644494</v>
+        <v>-10.49660884912284</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>3.188492285717647</v>
       </c>
       <c r="E38">
-        <v>-31.43024952604935</v>
+        <v>-31.90476114646908</v>
       </c>
       <c r="F38">
-        <v>2.881605917072812</v>
+        <v>2.928380510839289</v>
       </c>
       <c r="G38">
-        <v>-10.41965852860802</v>
+        <v>-9.38071002201854</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>3.122939635906027</v>
       </c>
       <c r="E39">
-        <v>-31.38055858076318</v>
+        <v>-31.6223315437957</v>
       </c>
       <c r="F39">
-        <v>2.245404841109541</v>
+        <v>2.972065294193324</v>
       </c>
       <c r="G39">
-        <v>-9.727900174904068</v>
+        <v>-9.369523688641344</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>3.026675785049828</v>
       </c>
       <c r="E40">
-        <v>-30.74237432428422</v>
+        <v>-31.15497264807108</v>
       </c>
       <c r="F40">
-        <v>2.255969838964846</v>
+        <v>2.530914920362836</v>
       </c>
       <c r="G40">
-        <v>-11.17132782493616</v>
+        <v>-9.708053454396136</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.899893861606047</v>
       </c>
       <c r="E41">
-        <v>-29.92405416449115</v>
+        <v>-31.34700938107736</v>
       </c>
       <c r="F41">
-        <v>2.387320744557153</v>
+        <v>2.963229927475064</v>
       </c>
       <c r="G41">
-        <v>-11.09616188846701</v>
+        <v>-9.08809090180236</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>2.746098570673551</v>
       </c>
       <c r="E42">
-        <v>-29.72202988206096</v>
+        <v>-29.9008230928318</v>
       </c>
       <c r="F42">
-        <v>2.676336474659095</v>
+        <v>2.707280967358073</v>
       </c>
       <c r="G42">
-        <v>-10.62547514478451</v>
+        <v>-10.22166142099529</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>2.564945436752808</v>
       </c>
       <c r="E43">
-        <v>-28.90843518489488</v>
+        <v>-30.44875033386388</v>
       </c>
       <c r="F43">
-        <v>2.470997449383542</v>
+        <v>2.810686070249535</v>
       </c>
       <c r="G43">
-        <v>-12.49440059188804</v>
+        <v>-8.985175972623038</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>2.355885267442455</v>
       </c>
       <c r="E44">
-        <v>-28.24652172461573</v>
+        <v>-30.14996161883779</v>
       </c>
       <c r="F44">
-        <v>2.236345815192526</v>
+        <v>3.03398078734817</v>
       </c>
       <c r="G44">
-        <v>-11.40778022953306</v>
+        <v>-9.804178454674416</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>2.122088819812709</v>
       </c>
       <c r="E45">
-        <v>-28.26994752065741</v>
+        <v>-29.48709265054302</v>
       </c>
       <c r="F45">
-        <v>2.301795123687715</v>
+        <v>2.83669680669744</v>
       </c>
       <c r="G45">
-        <v>-10.81072003097997</v>
+        <v>-10.28425721605183</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.864942614942332</v>
       </c>
       <c r="E46">
-        <v>-27.27528631876865</v>
+        <v>-29.21741749491224</v>
       </c>
       <c r="F46">
-        <v>2.68592234224429</v>
+        <v>3.071656593562297</v>
       </c>
       <c r="G46">
-        <v>-11.46645633867111</v>
+        <v>-10.38063712833663</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.588430782242713</v>
       </c>
       <c r="E47">
-        <v>-26.96504509297716</v>
+        <v>-28.75418177477161</v>
       </c>
       <c r="F47">
-        <v>2.155122734613229</v>
+        <v>3.142210301993536</v>
       </c>
       <c r="G47">
-        <v>-12.27079310398351</v>
+        <v>-10.90496464139194</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.298899773180721</v>
       </c>
       <c r="E48">
-        <v>-26.55895871481333</v>
+        <v>-27.81522986012521</v>
       </c>
       <c r="F48">
-        <v>2.094135012949518</v>
+        <v>2.670995161645843</v>
       </c>
       <c r="G48">
-        <v>-11.2868890380755</v>
+        <v>-10.23062306777009</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.001641063039503</v>
       </c>
       <c r="E49">
-        <v>-26.60144032947928</v>
+        <v>-27.82518797446808</v>
       </c>
       <c r="F49">
-        <v>2.566282894992764</v>
+        <v>2.697907161827994</v>
       </c>
       <c r="G49">
-        <v>-11.60520792331304</v>
+        <v>-10.0862270029837</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.7029757852066796</v>
       </c>
       <c r="E50">
-        <v>-25.24420685616639</v>
+        <v>-27.3634058944839</v>
       </c>
       <c r="F50">
-        <v>2.433371345213583</v>
+        <v>2.643455258972371</v>
       </c>
       <c r="G50">
-        <v>-11.90771233250948</v>
+        <v>-9.929734204796814</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.4080636224144807</v>
       </c>
       <c r="E51">
-        <v>-25.97125788657188</v>
+        <v>-25.41317327834059</v>
       </c>
       <c r="F51">
-        <v>2.040857735071065</v>
+        <v>2.90459642597011</v>
       </c>
       <c r="G51">
-        <v>-12.70330263650714</v>
+        <v>-10.03650923007493</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.1208248872699212</v>
       </c>
       <c r="E52">
-        <v>-25.49480355080286</v>
+        <v>-25.41876141526605</v>
       </c>
       <c r="F52">
-        <v>2.044293803057877</v>
+        <v>2.664447745694116</v>
       </c>
       <c r="G52">
-        <v>-11.9098972925654</v>
+        <v>-10.17325462412006</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.1563248884074474</v>
       </c>
       <c r="E53">
-        <v>-24.33147933449841</v>
+        <v>-25.18669523626898</v>
       </c>
       <c r="F53">
-        <v>2.520702807021123</v>
+        <v>2.529074287993815</v>
       </c>
       <c r="G53">
-        <v>-12.02578956025867</v>
+        <v>-10.40526096605773</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.4232740578042475</v>
       </c>
       <c r="E54">
-        <v>-23.88615825753212</v>
+        <v>-25.48354576441979</v>
       </c>
       <c r="F54">
-        <v>1.926011221612136</v>
+        <v>3.031527163101078</v>
       </c>
       <c r="G54">
-        <v>-11.13429606253387</v>
+        <v>-10.59559085020151</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.6813451095438348</v>
       </c>
       <c r="E55">
-        <v>-24.10189928773154</v>
+        <v>-23.50472489186605</v>
       </c>
       <c r="F55">
-        <v>1.774978306529313</v>
+        <v>1.999944669046797</v>
       </c>
       <c r="G55">
-        <v>-12.22785532833917</v>
+        <v>-9.855280035618605</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.9333506889684199</v>
       </c>
       <c r="E56">
-        <v>-23.06016459853305</v>
+        <v>-24.14816670666792</v>
       </c>
       <c r="F56">
-        <v>1.643711894412093</v>
+        <v>2.211670406997934</v>
       </c>
       <c r="G56">
-        <v>-11.73411725606672</v>
+        <v>-10.43469171590185</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.182375973907756</v>
       </c>
       <c r="E57">
-        <v>-23.01267449161461</v>
+        <v>-23.13511084335999</v>
       </c>
       <c r="F57">
-        <v>1.902046552649146</v>
+        <v>2.54208628315699</v>
       </c>
       <c r="G57">
-        <v>-12.17927969364144</v>
+        <v>-10.80644611668877</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.431010589330318</v>
       </c>
       <c r="E58">
-        <v>-22.56603562871209</v>
+        <v>-22.81992905242614</v>
       </c>
       <c r="F58">
-        <v>1.610825708520952</v>
+        <v>2.226740066789663</v>
       </c>
       <c r="G58">
-        <v>-12.04725182698976</v>
+        <v>-10.27573918237928</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.683222051475612</v>
       </c>
       <c r="E59">
-        <v>-22.78819350658038</v>
+        <v>-22.26380980191418</v>
       </c>
       <c r="F59">
-        <v>1.437998447070475</v>
+        <v>1.782844483386297</v>
       </c>
       <c r="G59">
-        <v>-12.41075303774728</v>
+        <v>-10.35679126881726</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.940147052463798</v>
       </c>
       <c r="E60">
-        <v>-22.21949868374912</v>
+        <v>-22.61819912080644</v>
       </c>
       <c r="F60">
-        <v>1.803699461119178</v>
+        <v>2.294657910145194</v>
       </c>
       <c r="G60">
-        <v>-11.72289781723413</v>
+        <v>-10.79728914772714</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.202972911856879</v>
       </c>
       <c r="E61">
-        <v>-21.99984958048108</v>
+        <v>-22.11301614593276</v>
       </c>
       <c r="F61">
-        <v>1.276405504336764</v>
+        <v>2.14128402878206</v>
       </c>
       <c r="G61">
-        <v>-11.48870320469501</v>
+        <v>-10.0030230619452</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.473311057306626</v>
       </c>
       <c r="E62">
-        <v>-21.70877285669005</v>
+        <v>-21.88285645449292</v>
       </c>
       <c r="F62">
-        <v>1.405453548549287</v>
+        <v>2.077221407319158</v>
       </c>
       <c r="G62">
-        <v>-12.47658323579569</v>
+        <v>-11.01505021220932</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.746362000583078</v>
       </c>
       <c r="E63">
-        <v>-20.55612678209569</v>
+        <v>-22.25096704962843</v>
       </c>
       <c r="F63">
-        <v>1.60475046198882</v>
+        <v>2.194536455638429</v>
       </c>
       <c r="G63">
-        <v>-12.04219000286022</v>
+        <v>-11.27778172729696</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.020602711065395</v>
       </c>
       <c r="E64">
-        <v>-20.71826426546632</v>
+        <v>-20.58973258770662</v>
       </c>
       <c r="F64">
-        <v>1.562520291794102</v>
+        <v>1.585961432558522</v>
       </c>
       <c r="G64">
-        <v>-11.84764248369941</v>
+        <v>-10.95943304714957</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.293209006342269</v>
       </c>
       <c r="E65">
-        <v>-21.60812299339557</v>
+        <v>-21.79449686965525</v>
       </c>
       <c r="F65">
-        <v>0.9961903495221637</v>
+        <v>2.261367480961488</v>
       </c>
       <c r="G65">
-        <v>-12.76411735806355</v>
+        <v>-10.58940344058861</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.555034737483404</v>
       </c>
       <c r="E66">
-        <v>-20.85012890009568</v>
+        <v>-20.90466531257005</v>
       </c>
       <c r="F66">
-        <v>1.18316115600804</v>
+        <v>1.760741984344801</v>
       </c>
       <c r="G66">
-        <v>-13.00509858895818</v>
+        <v>-10.87993360656951</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.803789037246338</v>
       </c>
       <c r="E67">
-        <v>-21.0130316955736</v>
+        <v>-22.81345333459517</v>
       </c>
       <c r="F67">
-        <v>1.317181061372167</v>
+        <v>1.80023522864067</v>
       </c>
       <c r="G67">
-        <v>-12.81228579565994</v>
+        <v>-12.71670372485011</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.033221633516852</v>
       </c>
       <c r="E68">
-        <v>-20.64184626658689</v>
+        <v>-20.79490415957214</v>
       </c>
       <c r="F68">
-        <v>0.9953553551801418</v>
+        <v>1.666730567801085</v>
       </c>
       <c r="G68">
-        <v>-13.25559763827821</v>
+        <v>-11.41108415398126</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.233057070613833</v>
       </c>
       <c r="E69">
-        <v>-21.40944072478304</v>
+        <v>-21.16495294158293</v>
       </c>
       <c r="F69">
-        <v>1.081305100159813</v>
+        <v>1.671718996300744</v>
       </c>
       <c r="G69">
-        <v>-11.73336576222931</v>
+        <v>-11.6183805840138</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.399216455344363</v>
       </c>
       <c r="E70">
-        <v>-20.38269075607593</v>
+        <v>-21.21370649274951</v>
       </c>
       <c r="F70">
-        <v>1.407444943785617</v>
+        <v>1.4999669557391</v>
       </c>
       <c r="G70">
-        <v>-11.5624058800358</v>
+        <v>-11.62588890129687</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.522907587664627</v>
       </c>
       <c r="E71">
-        <v>-20.84958095474075</v>
+        <v>-21.58482399462611</v>
       </c>
       <c r="F71">
-        <v>1.119434851710674</v>
+        <v>1.417956926127143</v>
       </c>
       <c r="G71">
-        <v>-12.32210987038776</v>
+        <v>-11.67676867568993</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.594709200532562</v>
       </c>
       <c r="E72">
-        <v>-21.38188043197236</v>
+        <v>-22.10455695648643</v>
       </c>
       <c r="F72">
-        <v>0.951778259588471</v>
+        <v>1.524519765558077</v>
       </c>
       <c r="G72">
-        <v>-11.72695985661082</v>
+        <v>-11.15649989146576</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.611346425482952</v>
       </c>
       <c r="E73">
-        <v>-20.76745255013764</v>
+        <v>-20.88622536641082</v>
       </c>
       <c r="F73">
-        <v>1.094616964322801</v>
+        <v>1.424797584139462</v>
       </c>
       <c r="G73">
-        <v>-12.26859490174544</v>
+        <v>-11.17672070361963</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.566174410479067</v>
       </c>
       <c r="E74">
-        <v>-20.49693962681544</v>
+        <v>-21.75802001152347</v>
       </c>
       <c r="F74">
-        <v>1.006377611841792</v>
+        <v>1.222772028475107</v>
       </c>
       <c r="G74">
-        <v>-12.44661948811974</v>
+        <v>-11.2067705254796</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.45661446983124</v>
       </c>
       <c r="E75">
-        <v>-20.0233065303532</v>
+        <v>-22.0920764821213</v>
       </c>
       <c r="F75">
-        <v>1.247212180327304</v>
+        <v>1.029699467700209</v>
       </c>
       <c r="G75">
-        <v>-11.69264274155073</v>
+        <v>-11.63125529561603</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.284962692171115</v>
       </c>
       <c r="E76">
-        <v>-21.99684267373999</v>
+        <v>-21.59234126147884</v>
       </c>
       <c r="F76">
-        <v>0.7083724386846699</v>
+        <v>0.8817298552729392</v>
       </c>
       <c r="G76">
-        <v>-11.51223787293369</v>
+        <v>-11.93493163793337</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.052015363285229</v>
       </c>
       <c r="E77">
-        <v>-20.90080705271551</v>
+        <v>-22.27847752922502</v>
       </c>
       <c r="F77">
-        <v>1.123742362205232</v>
+        <v>1.337451211718671</v>
       </c>
       <c r="G77">
-        <v>-11.00856485349789</v>
+        <v>-11.49376833937009</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.764007421092741</v>
       </c>
       <c r="E78">
-        <v>-22.34587933635519</v>
+        <v>-21.9980925325661</v>
       </c>
       <c r="F78">
-        <v>0.9679778125176182</v>
+        <v>1.398231841531681</v>
       </c>
       <c r="G78">
-        <v>-10.11252928729321</v>
+        <v>-11.13643798549778</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.428691285929782</v>
       </c>
       <c r="E79">
-        <v>-22.55584656219483</v>
+        <v>-22.89797277347433</v>
       </c>
       <c r="F79">
-        <v>0.5221695287811886</v>
+        <v>1.129572411986135</v>
       </c>
       <c r="G79">
-        <v>-10.55582126663824</v>
+        <v>-10.56679903564646</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.05207182584781</v>
       </c>
       <c r="E80">
-        <v>-23.21441348018232</v>
+        <v>-24.05276534474832</v>
       </c>
       <c r="F80">
-        <v>0.7413398045812846</v>
+        <v>0.9743960031545087</v>
       </c>
       <c r="G80">
-        <v>-10.14609159797034</v>
+        <v>-9.978839526780824</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.643100173692633</v>
       </c>
       <c r="E81">
-        <v>-23.28739436728993</v>
+        <v>-24.49330888163652</v>
       </c>
       <c r="F81">
-        <v>0.8201142311179064</v>
+        <v>1.015224575703691</v>
       </c>
       <c r="G81">
-        <v>-10.17217538627426</v>
+        <v>-9.658779294589625</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.208467943172856</v>
       </c>
       <c r="E82">
-        <v>-26.06959822812244</v>
+        <v>-25.1968616604162</v>
       </c>
       <c r="F82">
-        <v>0.6117823144160391</v>
+        <v>1.048937472262825</v>
       </c>
       <c r="G82">
-        <v>-9.732915651396063</v>
+        <v>-9.499926077433235</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.752263959756782</v>
       </c>
       <c r="E83">
-        <v>-25.97729887089811</v>
+        <v>-25.52105511462532</v>
       </c>
       <c r="F83">
-        <v>0.6526928953380983</v>
+        <v>1.006685764515634</v>
       </c>
       <c r="G83">
-        <v>-9.226246588247227</v>
+        <v>-9.523851390045548</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.281872413365914</v>
       </c>
       <c r="E84">
-        <v>-26.67553069271878</v>
+        <v>-26.52690164731303</v>
       </c>
       <c r="F84">
-        <v>1.045027578121611</v>
+        <v>0.5810449135677607</v>
       </c>
       <c r="G84">
-        <v>-8.872223469368643</v>
+        <v>-8.668906315074304</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.8023169145476606</v>
       </c>
       <c r="E85">
-        <v>-27.27777697947287</v>
+        <v>-27.37481764898324</v>
       </c>
       <c r="F85">
-        <v>0.6740308112668107</v>
+        <v>0.9192780929070352</v>
       </c>
       <c r="G85">
-        <v>-9.309251896553373</v>
+        <v>-9.50031672180687</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.3182807424751341</v>
       </c>
       <c r="E86">
-        <v>-28.24580169724851</v>
+        <v>-28.8951033574163</v>
       </c>
       <c r="F86">
-        <v>0.8545196428257811</v>
+        <v>1.083081119871415</v>
       </c>
       <c r="G86">
-        <v>-9.220873572836989</v>
+        <v>-8.245474298419362</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.1607773461355459</v>
       </c>
       <c r="E87">
-        <v>-29.57113433541437</v>
+        <v>-29.51153961747343</v>
       </c>
       <c r="F87">
-        <v>0.3436969434806323</v>
+        <v>0.8376176343390599</v>
       </c>
       <c r="G87">
-        <v>-8.314333645636204</v>
+        <v>-7.963770046846159</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.6269025892352418</v>
       </c>
       <c r="E88">
-        <v>-31.28119933256089</v>
+        <v>-31.39136125550848</v>
       </c>
       <c r="F88">
-        <v>0.7541662454462321</v>
+        <v>0.7576586424164349</v>
       </c>
       <c r="G88">
-        <v>-8.067611928776479</v>
+        <v>-7.864119315568557</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.070207187357578</v>
       </c>
       <c r="E89">
-        <v>-31.54361760859437</v>
+        <v>-32.81507272725397</v>
       </c>
       <c r="F89">
-        <v>0.6836141937497983</v>
+        <v>0.5329383050175822</v>
       </c>
       <c r="G89">
-        <v>-7.951782561448458</v>
+        <v>-8.150743037813116</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.477979682596752</v>
       </c>
       <c r="E90">
-        <v>-33.08219155930742</v>
+        <v>-34.34151716033747</v>
       </c>
       <c r="F90">
-        <v>0.4932156029511375</v>
+        <v>0.3717719714963132</v>
       </c>
       <c r="G90">
-        <v>-7.740808115321784</v>
+        <v>-7.812746269890146</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.838676110155277</v>
       </c>
       <c r="E91">
-        <v>-34.38927671145937</v>
+        <v>-35.41286127683512</v>
       </c>
       <c r="F91">
-        <v>0.5466983159454848</v>
+        <v>0.4450418966413323</v>
       </c>
       <c r="G91">
-        <v>-8.384629769617087</v>
+        <v>-8.230573532947103</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.13907987374423</v>
       </c>
       <c r="E92">
-        <v>-36.48653755744672</v>
+        <v>-37.63245884813969</v>
       </c>
       <c r="F92">
-        <v>0.3504009208714887</v>
+        <v>0.4352911839429793</v>
       </c>
       <c r="G92">
-        <v>-8.82145625352392</v>
+        <v>-7.739566660744557</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.365656933055638</v>
       </c>
       <c r="E93">
-        <v>-38.20914869183149</v>
+        <v>-38.80016889152056</v>
       </c>
       <c r="F93">
-        <v>0.2610424440292977</v>
+        <v>0.4609664315927499</v>
       </c>
       <c r="G93">
-        <v>-9.037618324510632</v>
+        <v>-7.710602697821473</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.506936072394744</v>
       </c>
       <c r="E94">
-        <v>-40.703830680969</v>
+        <v>-40.74741950752983</v>
       </c>
       <c r="F94">
-        <v>0.1378012553103984</v>
+        <v>0.21557252892223</v>
       </c>
       <c r="G94">
-        <v>-7.950223294499462</v>
+        <v>-7.765693486140485</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.553517068628068</v>
       </c>
       <c r="E95">
-        <v>-41.61345846217873</v>
+        <v>-43.49477223239931</v>
       </c>
       <c r="F95">
-        <v>-0.09193318997759968</v>
+        <v>-0.01638276937267357</v>
       </c>
       <c r="G95">
-        <v>-8.608313400069024</v>
+        <v>-7.968613374970113</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.491252760951846</v>
       </c>
       <c r="E96">
-        <v>-45.89381737896883</v>
+        <v>-44.69057240004977</v>
       </c>
       <c r="F96">
-        <v>-0.3718998345713598</v>
+        <v>0.225558497962978</v>
       </c>
       <c r="G96">
-        <v>-8.940890804944207</v>
+        <v>-8.88972632363477</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.324395780900261</v>
       </c>
       <c r="E97">
-        <v>-46.42765427312604</v>
+        <v>-46.82493503358197</v>
       </c>
       <c r="F97">
-        <v>-0.5145057680655031</v>
+        <v>-0.1567098641417154</v>
       </c>
       <c r="G97">
-        <v>-8.765388854270823</v>
+        <v>-8.824965431795547</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.033922461211203</v>
       </c>
       <c r="E98">
-        <v>-47.93974117936823</v>
+        <v>-49.75860502878604</v>
       </c>
       <c r="F98">
-        <v>-0.5754280487043927</v>
+        <v>-0.5144270731622371</v>
       </c>
       <c r="G98">
-        <v>-8.825902316183161</v>
+        <v>-8.951352128848304</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.647974325769932</v>
       </c>
       <c r="E99">
-        <v>-50.89211603646098</v>
+        <v>-51.88024151823817</v>
       </c>
       <c r="F99">
-        <v>-0.9856364149381107</v>
+        <v>-0.8199008068229996</v>
       </c>
       <c r="G99">
-        <v>-9.283197903159309</v>
+        <v>-9.865387131149999</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.130399324622992</v>
       </c>
       <c r="E100">
-        <v>-52.72784165884634</v>
+        <v>-54.38317099066215</v>
       </c>
       <c r="F100">
-        <v>-1.238479825662007</v>
+        <v>-1.270178961064935</v>
       </c>
       <c r="G100">
-        <v>-9.779524822043463</v>
+        <v>-9.560466023709887</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.5569786115978429</v>
       </c>
       <c r="E101">
-        <v>-55.22092283242214</v>
+        <v>-55.58343736580267</v>
       </c>
       <c r="F101">
-        <v>-1.751558169444978</v>
+        <v>-1.34143263995154</v>
       </c>
       <c r="G101">
-        <v>-10.08429695493431</v>
+        <v>-10.44586480709689</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.1720593930123869</v>
       </c>
       <c r="E102">
-        <v>-56.77688612332464</v>
+        <v>-58.22868998357671</v>
       </c>
       <c r="F102">
-        <v>-1.678236885520986</v>
+        <v>-1.31491411428572</v>
       </c>
       <c r="G102">
-        <v>-10.64179944483865</v>
+        <v>-11.51096331290107</v>
       </c>
     </row>
   </sheetData>
